--- a/apps/home/homepage/fixtures/hamouds.xlsx
+++ b/apps/home/homepage/fixtures/hamouds.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Backup\ng\backend\api\apps\home\homepage\fixtures\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\muhammad.hamoud\Desktop\ng\backend\project\apps\home\homepage\fixtures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F21933B-7931-4218-A4F7-30ACF9B49C04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D15A97BE-6C55-4B97-A0DA-3E2FC9B0849D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="480" windowWidth="29040" windowHeight="15840" tabRatio="660" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="660" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="site" sheetId="1" r:id="rId1"/>
@@ -1025,7 +1025,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1049,34 +1049,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1104,10 +1089,10 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1128,7 +1113,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1140,18 +1125,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1649,10 +1622,10 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE354C8F-D76E-4D6E-B370-894F46303512}">
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.5703125" style="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.5703125" style="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="47.85546875" style="4" customWidth="1"/>
     <col min="3" max="3" width="10.42578125" style="4" customWidth="1"/>
     <col min="4" max="4" width="24.140625" style="4" bestFit="1" customWidth="1"/>
@@ -1661,224 +1634,187 @@
     <col min="7" max="7" width="6.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="47" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="47" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="47" t="s">
+      <c r="C1" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D1" s="47" t="s">
+      <c r="D1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="47" t="s">
+      <c r="E1" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="47" t="s">
+      <c r="F1" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="G1" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-    </row>
-    <row r="2" spans="1:10" ht="48.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="34" t="s">
+    </row>
+    <row r="2" spans="1:7" ht="48.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="27" t="s">
         <v>260</v>
       </c>
-      <c r="B2" s="34" t="s">
+      <c r="B2" s="27" t="s">
         <v>142</v>
       </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="34" t="s">
+      <c r="D2" s="27" t="s">
         <v>260</v>
       </c>
-      <c r="E2" s="34" t="s">
+      <c r="E2" s="27" t="s">
         <v>261</v>
       </c>
-      <c r="F2" s="22" t="s">
+      <c r="F2" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="G2" s="18" t="s">
+      <c r="G2" s="14" t="s">
         <v>271</v>
       </c>
-      <c r="H2" s="17"/>
-      <c r="I2" s="17"/>
-      <c r="J2" s="17"/>
-    </row>
-    <row r="3" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="34" t="s">
+    </row>
+    <row r="3" spans="1:7" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="27" t="s">
         <v>133</v>
       </c>
-      <c r="B3" s="34" t="s">
+      <c r="B3" s="27" t="s">
         <v>134</v>
       </c>
-      <c r="C3" s="48"/>
-      <c r="D3" s="34" t="s">
+      <c r="D3" s="27" t="s">
         <v>187</v>
       </c>
-      <c r="E3" s="34" t="s">
+      <c r="E3" s="27" t="s">
         <v>188</v>
       </c>
-      <c r="F3" s="22" t="s">
+      <c r="F3" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="G3" s="18" t="str">
+      <c r="G3" s="14" t="str">
         <f>SUBSTITUTE(TRIM(LOWER(A3)), " ", "_")</f>
         <v>tailored_web_solutions</v>
       </c>
-      <c r="H3" s="17"/>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
-    </row>
-    <row r="4" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="34" t="s">
+    </row>
+    <row r="4" spans="1:7" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="27" t="s">
         <v>135</v>
       </c>
-      <c r="B4" s="34" t="s">
+      <c r="B4" s="27" t="s">
         <v>136</v>
       </c>
-      <c r="C4" s="48"/>
-      <c r="D4" s="34" t="s">
+      <c r="D4" s="27" t="s">
         <v>148</v>
       </c>
-      <c r="E4" s="34" t="s">
+      <c r="E4" s="27" t="s">
         <v>189</v>
       </c>
-      <c r="F4" s="22" t="s">
+      <c r="F4" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="G4" s="18" t="str">
+      <c r="G4" s="14" t="str">
         <f t="shared" ref="G4:G7" si="0">SUBSTITUTE(TRIM(LOWER(A4)), " ", "_")</f>
         <v>scalable_e-commerce_solutions</v>
       </c>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17"/>
-    </row>
-    <row r="5" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="34" t="s">
+    </row>
+    <row r="5" spans="1:7" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="27" t="s">
         <v>137</v>
       </c>
-      <c r="B5" s="34" t="s">
+      <c r="B5" s="27" t="s">
         <v>138</v>
       </c>
-      <c r="C5" s="49"/>
-      <c r="D5" s="34" t="s">
+      <c r="C5" s="3"/>
+      <c r="D5" s="27" t="s">
         <v>273</v>
       </c>
-      <c r="E5" s="34" t="s">
+      <c r="E5" s="27" t="s">
         <v>190</v>
       </c>
-      <c r="F5" s="22" t="s">
+      <c r="F5" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="G5" s="18" t="str">
+      <c r="G5" s="14" t="str">
         <f t="shared" si="0"/>
         <v>intuitive_content_management</v>
       </c>
-      <c r="H5" s="17"/>
-      <c r="I5" s="17"/>
-      <c r="J5" s="17"/>
-    </row>
-    <row r="6" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="34" t="s">
+    </row>
+    <row r="6" spans="1:7" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="27" t="s">
         <v>139</v>
       </c>
-      <c r="B6" s="34" t="s">
+      <c r="B6" s="27" t="s">
         <v>140</v>
       </c>
-      <c r="C6" s="48"/>
-      <c r="D6" s="34" t="s">
+      <c r="D6" s="27" t="s">
         <v>274</v>
       </c>
-      <c r="E6" s="34" t="s">
+      <c r="E6" s="27" t="s">
         <v>191</v>
       </c>
-      <c r="F6" s="22" t="s">
+      <c r="F6" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="G6" s="18" t="str">
+      <c r="G6" s="14" t="str">
         <f t="shared" si="0"/>
         <v>seamless_responsive_websites</v>
       </c>
-      <c r="H6" s="17"/>
-      <c r="I6" s="17"/>
-      <c r="J6" s="17"/>
-    </row>
-    <row r="7" spans="1:10" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="34" t="s">
+    </row>
+    <row r="7" spans="1:7" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="B7" s="34" t="s">
+      <c r="B7" s="27" t="s">
         <v>141</v>
       </c>
-      <c r="C7" s="49"/>
-      <c r="D7" s="34" t="s">
+      <c r="C7" s="3"/>
+      <c r="D7" s="27" t="s">
         <v>275</v>
       </c>
-      <c r="E7" s="34" t="s">
+      <c r="E7" s="27" t="s">
         <v>192</v>
       </c>
-      <c r="F7" s="22" t="s">
+      <c r="F7" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="G7" s="18" t="str">
+      <c r="G7" s="14" t="str">
         <f t="shared" si="0"/>
         <v>mobile_app_development</v>
       </c>
-      <c r="H7" s="17"/>
-      <c r="I7" s="17"/>
-      <c r="J7" s="17"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="50"/>
-      <c r="B8" s="49"/>
-      <c r="C8" s="49"/>
-      <c r="D8" s="48"/>
-      <c r="E8" s="48"/>
-      <c r="F8" s="50"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="17"/>
-      <c r="I8" s="17"/>
-      <c r="J8" s="17"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="50"/>
-      <c r="B9" s="49"/>
-      <c r="C9" s="49"/>
-      <c r="D9" s="48"/>
-      <c r="E9" s="48"/>
-      <c r="F9" s="50"/>
-      <c r="G9" s="17"/>
-      <c r="H9" s="17"/>
-      <c r="I9" s="17"/>
-      <c r="J9" s="17"/>
-    </row>
-    <row r="10" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="5"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="F8" s="5"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="5"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="F9" s="5"/>
+    </row>
+    <row r="10" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5"/>
       <c r="C10" s="3"/>
-      <c r="E10" s="46"/>
+      <c r="E10" s="39"/>
       <c r="F10" s="5"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="5"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
       <c r="F11" s="5"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="5"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
       <c r="F12" s="5"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -1886,7 +1822,7 @@
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D14" s="3"/>
     </row>
     <row r="17" spans="4:4" x14ac:dyDescent="0.25">
@@ -1923,11 +1859,11 @@
       <c r="D27" s="3"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="A8:A13">
+    <cfRule type="duplicateValues" dxfId="3" priority="6"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="G1">
-    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A8:A13">
-    <cfRule type="duplicateValues" dxfId="2" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2013,66 +1949,66 @@
   <sheetData>
     <row r="2" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="25" t="s">
+      <c r="B3" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="C3" s="26" t="s">
+      <c r="C3" s="19" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="4" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="27" t="s">
+      <c r="B4" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="C4" s="28" t="s">
+      <c r="C4" s="21" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="5" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="27" t="s">
+      <c r="B5" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="C5" s="28" t="s">
+      <c r="C5" s="21" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="27" t="s">
+      <c r="B6" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="C6" s="28" t="s">
+      <c r="C6" s="21" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="7" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="27" t="s">
+      <c r="B7" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="C7" s="28" t="s">
+      <c r="C7" s="21" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="8" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="27" t="s">
+      <c r="B8" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="C8" s="28" t="s">
+      <c r="C8" s="21" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="27" t="s">
+      <c r="B9" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="C9" s="28" t="s">
+      <c r="C9" s="21" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="10" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="27" t="s">
+      <c r="B10" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="C10" s="28" t="s">
+      <c r="C10" s="21" t="s">
         <v>82</v>
       </c>
     </row>
@@ -2155,10 +2091,10 @@
       <c r="A2" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="9">
         <v>97143202204</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="9" t="s">
         <v>43</v>
       </c>
       <c r="E2" s="6" t="s">
@@ -2186,8 +2122,8 @@
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
@@ -2215,142 +2151,141 @@
   <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="4" width="23.85546875" customWidth="1"/>
-    <col min="5" max="7" width="23.85546875" style="9" customWidth="1"/>
+    <col min="1" max="7" width="23.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="E1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="16" t="s">
+      <c r="F1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="16" t="s">
+      <c r="G1" s="8" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:7" s="17" customFormat="1" ht="200.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="18" t="s">
+    <row r="2" spans="1:7" ht="200.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="14" t="s">
         <v>194</v>
       </c>
-      <c r="B2" s="34" t="s">
+      <c r="B2" s="27" t="s">
         <v>200</v>
       </c>
-      <c r="C2" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="D2" s="33" t="s">
+      <c r="C2" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" s="26" t="s">
         <v>193</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="14" t="s">
         <v>195</v>
       </c>
-      <c r="F2" s="34" t="s">
+      <c r="F2" s="27" t="s">
         <v>201</v>
       </c>
-      <c r="G2" s="35" t="s">
+      <c r="G2" s="28" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="3" spans="1:7" s="17" customFormat="1" ht="171.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="18" t="s">
+    <row r="3" spans="1:7" ht="171.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="14" t="s">
         <v>196</v>
       </c>
-      <c r="B3" s="34" t="s">
+      <c r="B3" s="27" t="s">
         <v>197</v>
       </c>
-      <c r="C3" s="22" t="s">
-        <v>56</v>
-      </c>
-      <c r="D3" s="17" t="s">
+      <c r="C3" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" t="s">
         <v>198</v>
       </c>
-      <c r="E3" s="18" t="s">
+      <c r="E3" s="14" t="s">
         <v>199</v>
       </c>
-      <c r="F3" s="34" t="s">
+      <c r="F3" s="27" t="s">
         <v>202</v>
       </c>
-      <c r="G3" s="16" t="s">
+      <c r="G3" s="8" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="4" spans="1:7" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="18"/>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
-    </row>
-    <row r="5" spans="1:7" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="18"/>
-      <c r="B5" s="18"/>
-      <c r="C5" s="18"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="18"/>
-      <c r="G5" s="18"/>
-    </row>
-    <row r="6" spans="1:7" s="17" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="18"/>
-      <c r="B6" s="18"/>
-      <c r="C6" s="22"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
-    </row>
-    <row r="7" spans="1:7" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="18"/>
-      <c r="B7" s="18"/>
-      <c r="C7" s="18"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="18"/>
-      <c r="G7" s="18"/>
-    </row>
-    <row r="8" spans="1:7" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="18"/>
-      <c r="B8" s="18"/>
-      <c r="C8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="18"/>
-    </row>
-    <row r="9" spans="1:7" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="18"/>
-      <c r="B9" s="18"/>
-      <c r="C9" s="18"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="18"/>
-    </row>
-    <row r="10" spans="1:7" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="18"/>
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
-      <c r="G10" s="18"/>
-    </row>
-    <row r="11" spans="1:7" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="18"/>
-      <c r="B11" s="18"/>
-      <c r="C11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="14"/>
+      <c r="B5" s="14"/>
+      <c r="C5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14"/>
+    </row>
+    <row r="6" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="14"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="15"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="14"/>
+      <c r="B7" s="14"/>
+      <c r="C7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="14"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="14"/>
+      <c r="B8" s="14"/>
+      <c r="C8" s="14"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="14"/>
+      <c r="B9" s="14"/>
+      <c r="C9" s="14"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="14"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="14"/>
+      <c r="B10" s="14"/>
+      <c r="C10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="14"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="14"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="14"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:C1">
@@ -2379,142 +2314,142 @@
     <col min="5" max="5" width="26.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="21" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+    <row r="1" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="20" t="s">
+      <c r="D1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="20" t="s">
+      <c r="E1" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="F1" s="20" t="s">
+      <c r="F1" s="8" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:6" s="21" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="22" t="s">
+    <row r="2" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="C2" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="E2" s="21" t="s">
+      <c r="E2" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="3" spans="1:6" s="21" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="22" t="s">
+    <row r="3" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="C3" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="E3" s="21" t="s">
+      <c r="E3" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="4" spans="1:6" s="21" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="22" t="s">
+    <row r="4" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="C4" s="22" t="s">
+      <c r="C4" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="E4" s="21" t="s">
+      <c r="E4" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="5" spans="1:6" s="21" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="22" t="s">
+    <row r="5" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="C5" s="22" t="s">
+      <c r="C5" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="E5" s="21" t="s">
+      <c r="E5" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="6" spans="1:6" s="21" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="22" t="s">
+    <row r="6" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="C6" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="E6" s="21" t="s">
+      <c r="E6" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="7" spans="1:6" s="21" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="22" t="s">
+    <row r="7" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="C7" s="22" t="s">
+      <c r="C7" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="E7" s="21" t="s">
+      <c r="E7" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="8" spans="1:6" s="21" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="22" t="s">
+    <row r="8" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="C8" s="22" t="s">
+      <c r="C8" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="E8" s="21" t="s">
+      <c r="E8" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="9" spans="1:6" s="21" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="22" t="s">
+    <row r="9" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="C9" s="22" t="s">
+      <c r="C9" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="E9" s="21" t="s">
+      <c r="E9" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="10" spans="1:6" s="21" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="22" t="s">
+    <row r="10" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="C10" s="22" t="s">
+      <c r="C10" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="E10" s="21" t="s">
+      <c r="E10" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="11" spans="1:6" s="21" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="22" t="s">
+    <row r="11" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="C11" s="22" t="s">
+      <c r="C11" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="E11" s="21" t="s">
+      <c r="E11" t="s">
         <v>212</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="A1:B1">
+    <cfRule type="duplicateValues" dxfId="11" priority="5"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="C1:F1">
-    <cfRule type="duplicateValues" dxfId="11" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:B1">
-    <cfRule type="duplicateValues" dxfId="10" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2614,7 +2549,7 @@
       <c r="J2" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="K2" s="10" t="s">
+      <c r="K2" s="9" t="s">
         <v>267</v>
       </c>
       <c r="L2" t="s">
@@ -2657,10 +2592,10 @@
       <c r="J3" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="K3" s="10" t="s">
+      <c r="K3" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="L3" s="10" t="s">
+      <c r="L3" s="9" t="s">
         <v>111</v>
       </c>
       <c r="M3" t="str">
@@ -2700,7 +2635,7 @@
       <c r="J4" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="K4" s="10">
+      <c r="K4" s="9">
         <v>96181525921</v>
       </c>
       <c r="L4" t="s">
@@ -2755,7 +2690,7 @@
       <c r="F12" s="7"/>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="C13" s="13"/>
+      <c r="C13" s="12"/>
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
       <c r="F13" s="7"/>
@@ -2809,29 +2744,28 @@
   <dimension ref="A1:G13"/>
   <sheetFormatPr defaultColWidth="30.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="39.28515625" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="75.85546875" style="11" customWidth="1"/>
-    <col min="3" max="3" width="6.42578125" style="11" customWidth="1"/>
-    <col min="4" max="4" width="18.7109375" style="14" customWidth="1"/>
-    <col min="5" max="5" width="77.28515625" style="14" customWidth="1"/>
-    <col min="6" max="6" width="40.7109375" style="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="30.140625" style="9"/>
+    <col min="1" max="1" width="39.28515625" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="75.85546875" style="10" customWidth="1"/>
+    <col min="3" max="3" width="6.42578125" style="10" customWidth="1"/>
+    <col min="4" max="4" width="18.7109375" style="13" customWidth="1"/>
+    <col min="5" max="5" width="77.28515625" style="13" customWidth="1"/>
+    <col min="6" max="6" width="40.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="10" t="s">
         <v>6</v>
       </c>
       <c r="F1" s="7" t="s">
@@ -2839,183 +2773,183 @@
       </c>
     </row>
     <row r="2" spans="1:7" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="D2" s="24" t="s">
+      <c r="D2" s="17" t="s">
         <v>146</v>
       </c>
-      <c r="E2" s="24" t="s">
+      <c r="E2" s="17" t="s">
         <v>155</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="F2" t="s">
         <v>214</v>
       </c>
-      <c r="G2" s="42" t="s">
+      <c r="G2" s="35" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="D3" s="24" t="s">
+      <c r="D3" s="17" t="s">
         <v>147</v>
       </c>
-      <c r="E3" s="24" t="s">
+      <c r="E3" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="B4" s="24" t="s">
+      <c r="B4" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="D4" s="24" t="s">
+      <c r="D4" s="17" t="s">
         <v>148</v>
       </c>
-      <c r="E4" s="24" t="s">
+      <c r="E4" s="17" t="s">
         <v>157</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="23" t="s">
+      <c r="A5" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="B5" s="24" t="s">
+      <c r="B5" s="17" t="s">
         <v>121</v>
       </c>
-      <c r="D5" s="24" t="s">
+      <c r="D5" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="E5" s="24" t="s">
+      <c r="E5" s="17" t="s">
         <v>158</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="D6" s="24" t="s">
+      <c r="D6" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="E6" s="24" t="s">
+      <c r="E6" s="17" t="s">
         <v>159</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="F6" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="23" t="s">
+      <c r="A7" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="B7" s="24" t="s">
+      <c r="B7" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="D7" s="24" t="s">
+      <c r="D7" s="17" t="s">
         <v>150</v>
       </c>
-      <c r="E7" s="24" t="s">
+      <c r="E7" s="17" t="s">
         <v>160</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="F7" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="23" t="s">
+      <c r="A8" s="16" t="s">
         <v>125</v>
       </c>
-      <c r="B8" s="24" t="s">
+      <c r="B8" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="D8" s="24" t="s">
+      <c r="D8" s="17" t="s">
         <v>151</v>
       </c>
-      <c r="E8" s="24" t="s">
+      <c r="E8" s="17" t="s">
         <v>161</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="F8" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="23" t="s">
+      <c r="A9" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="B9" s="24" t="s">
+      <c r="B9" s="17" t="s">
         <v>127</v>
       </c>
-      <c r="D9" s="24" t="s">
+      <c r="D9" s="17" t="s">
         <v>152</v>
       </c>
-      <c r="E9" s="24" t="s">
+      <c r="E9" s="17" t="s">
         <v>163</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="F9" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="23" t="s">
+      <c r="A10" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="B10" s="24" t="s">
+      <c r="B10" s="17" t="s">
         <v>129</v>
       </c>
-      <c r="D10" s="24" t="s">
+      <c r="D10" s="17" t="s">
         <v>153</v>
       </c>
-      <c r="E10" s="24" t="s">
+      <c r="E10" s="17" t="s">
         <v>164</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="F10" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="23" t="s">
+      <c r="A11" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="17" t="s">
         <v>131</v>
       </c>
-      <c r="D11" s="24" t="s">
+      <c r="D11" s="17" t="s">
         <v>154</v>
       </c>
-      <c r="E11" s="24" t="s">
+      <c r="E11" s="17" t="s">
         <v>162</v>
       </c>
-      <c r="F11" s="9" t="s">
+      <c r="F11" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E12" s="24"/>
+      <c r="E12" s="17"/>
     </row>
     <row r="13" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E13" s="24"/>
+      <c r="E13" s="17"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A12:A21">
@@ -3063,17 +2997,17 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="33" t="s">
         <v>101</v>
       </c>
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="22" t="s">
         <v>102</v>
       </c>
       <c r="C2" s="8"/>
-      <c r="D2" s="23" t="s">
+      <c r="D2" s="16" t="s">
         <v>165</v>
       </c>
-      <c r="E2" s="24" t="s">
+      <c r="E2" s="17" t="s">
         <v>166</v>
       </c>
       <c r="F2" t="str">
@@ -3082,17 +3016,17 @@
       </c>
     </row>
     <row r="3" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="41" t="s">
+      <c r="A3" s="34" t="s">
         <v>103</v>
       </c>
-      <c r="B3" s="29" t="s">
+      <c r="B3" s="22" t="s">
         <v>104</v>
       </c>
       <c r="C3" s="8"/>
-      <c r="D3" s="23" t="s">
+      <c r="D3" s="16" t="s">
         <v>167</v>
       </c>
-      <c r="E3" s="24" t="s">
+      <c r="E3" s="17" t="s">
         <v>168</v>
       </c>
       <c r="F3" t="str">
@@ -3101,16 +3035,16 @@
       </c>
     </row>
     <row r="4" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="41" t="s">
+      <c r="A4" s="34" t="s">
         <v>105</v>
       </c>
-      <c r="B4" s="29" t="s">
+      <c r="B4" s="22" t="s">
         <v>106</v>
       </c>
-      <c r="D4" s="23" t="s">
+      <c r="D4" s="16" t="s">
         <v>169</v>
       </c>
-      <c r="E4" s="24" t="s">
+      <c r="E4" s="17" t="s">
         <v>170</v>
       </c>
       <c r="F4" t="str">
@@ -3119,16 +3053,16 @@
       </c>
     </row>
     <row r="5" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="41" t="s">
+      <c r="A5" s="34" t="s">
         <v>107</v>
       </c>
-      <c r="B5" s="29" t="s">
+      <c r="B5" s="22" t="s">
         <v>108</v>
       </c>
-      <c r="D5" s="23" t="s">
+      <c r="D5" s="16" t="s">
         <v>171</v>
       </c>
-      <c r="E5" s="24" t="s">
+      <c r="E5" s="17" t="s">
         <v>172</v>
       </c>
       <c r="F5" t="str">
@@ -3138,8 +3072,8 @@
     </row>
     <row r="8" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="9" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D9" s="32"/>
-      <c r="E9" s="31"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="24"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F1">
@@ -3183,179 +3117,179 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="36" t="s">
+      <c r="A2" s="29" t="s">
         <v>87</v>
       </c>
-      <c r="B2" s="37" t="s">
+      <c r="B2" s="30" t="s">
         <v>88</v>
       </c>
-      <c r="C2" s="11"/>
-      <c r="D2" s="38" t="s">
+      <c r="C2" s="10"/>
+      <c r="D2" s="31" t="s">
         <v>173</v>
       </c>
-      <c r="E2" s="39" t="s">
+      <c r="E2" s="32" t="s">
         <v>174</v>
       </c>
-      <c r="F2" s="18" t="str">
+      <c r="F2" s="14" t="str">
         <f>SUBSTITUTE(TRIM(LOWER(A2)), " ", "_")</f>
         <v>modern_design_aesthetics</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="36" t="s">
+      <c r="A3" s="29" t="s">
         <v>89</v>
       </c>
-      <c r="B3" s="37" t="s">
+      <c r="B3" s="30" t="s">
         <v>90</v>
       </c>
-      <c r="C3" s="11"/>
-      <c r="D3" s="38" t="s">
+      <c r="C3" s="10"/>
+      <c r="D3" s="31" t="s">
         <v>175</v>
       </c>
-      <c r="E3" s="39" t="s">
+      <c r="E3" s="32" t="s">
         <v>176</v>
       </c>
-      <c r="F3" s="18" t="str">
+      <c r="F3" s="14" t="str">
         <f t="shared" ref="F3:F8" si="0">SUBSTITUTE(TRIM(LOWER(A3)), " ", "_")</f>
         <v>cross-platform_compatibility</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="36" t="s">
+      <c r="A4" s="29" t="s">
         <v>93</v>
       </c>
-      <c r="B4" s="37" t="s">
+      <c r="B4" s="30" t="s">
         <v>91</v>
       </c>
-      <c r="C4" s="11"/>
-      <c r="D4" s="38" t="s">
+      <c r="C4" s="10"/>
+      <c r="D4" s="31" t="s">
         <v>177</v>
       </c>
-      <c r="E4" s="39" t="s">
+      <c r="E4" s="32" t="s">
         <v>178</v>
       </c>
-      <c r="F4" s="18" t="str">
+      <c r="F4" s="14" t="str">
         <f t="shared" si="0"/>
         <v>scalability</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="B5" s="37" t="s">
+      <c r="B5" s="30" t="s">
         <v>92</v>
       </c>
-      <c r="C5" s="11"/>
-      <c r="D5" s="38" t="s">
+      <c r="C5" s="10"/>
+      <c r="D5" s="31" t="s">
         <v>179</v>
       </c>
-      <c r="E5" s="39" t="s">
+      <c r="E5" s="32" t="s">
         <v>180</v>
       </c>
-      <c r="F5" s="18" t="str">
+      <c r="F5" s="14" t="str">
         <f t="shared" si="0"/>
         <v>performance</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="36" t="s">
+      <c r="A6" s="29" t="s">
         <v>95</v>
       </c>
-      <c r="B6" s="37" t="s">
+      <c r="B6" s="30" t="s">
         <v>96</v>
       </c>
-      <c r="C6" s="11"/>
-      <c r="D6" s="38" t="s">
+      <c r="C6" s="10"/>
+      <c r="D6" s="31" t="s">
         <v>181</v>
       </c>
-      <c r="E6" s="39" t="s">
+      <c r="E6" s="32" t="s">
         <v>182</v>
       </c>
-      <c r="F6" s="18" t="str">
+      <c r="F6" s="14" t="str">
         <f t="shared" si="0"/>
         <v>user-friendly_cms</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="36" t="s">
+      <c r="A7" s="29" t="s">
         <v>97</v>
       </c>
-      <c r="B7" s="37" t="s">
+      <c r="B7" s="30" t="s">
         <v>98</v>
       </c>
-      <c r="C7" s="11"/>
-      <c r="D7" s="38" t="s">
+      <c r="C7" s="10"/>
+      <c r="D7" s="31" t="s">
         <v>183</v>
       </c>
-      <c r="E7" s="39" t="s">
+      <c r="E7" s="32" t="s">
         <v>184</v>
       </c>
-      <c r="F7" s="18" t="str">
+      <c r="F7" s="14" t="str">
         <f t="shared" si="0"/>
         <v>seo_optimization</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="36" t="s">
+      <c r="A8" s="29" t="s">
         <v>99</v>
       </c>
-      <c r="B8" s="37" t="s">
+      <c r="B8" s="30" t="s">
         <v>132</v>
       </c>
-      <c r="C8" s="11"/>
-      <c r="D8" s="38" t="s">
+      <c r="C8" s="10"/>
+      <c r="D8" s="31" t="s">
         <v>185</v>
       </c>
-      <c r="E8" s="39" t="s">
+      <c r="E8" s="32" t="s">
         <v>186</v>
       </c>
-      <c r="F8" s="18" t="str">
+      <c r="F8" s="14" t="str">
         <f t="shared" si="0"/>
         <v>accessibility</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="29"/>
-      <c r="B9" s="30"/>
-      <c r="D9" s="23"/>
-      <c r="E9" s="24"/>
+      <c r="A9" s="22"/>
+      <c r="B9" s="23"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="17"/>
     </row>
     <row r="10" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="29"/>
-      <c r="B10" s="30"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="24"/>
+      <c r="A10" s="22"/>
+      <c r="B10" s="23"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="17"/>
     </row>
     <row r="11" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="29"/>
-      <c r="B11" s="30"/>
-      <c r="D11" s="23"/>
-      <c r="E11" s="24"/>
+      <c r="A11" s="22"/>
+      <c r="B11" s="23"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="17"/>
     </row>
     <row r="12" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="29"/>
-      <c r="B12" s="30"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="24"/>
+      <c r="A12" s="22"/>
+      <c r="B12" s="23"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="17"/>
     </row>
     <row r="13" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="29"/>
-      <c r="B13" s="30"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="24"/>
+      <c r="A13" s="22"/>
+      <c r="B13" s="23"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="17"/>
     </row>
     <row r="14" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="29"/>
-      <c r="B14" s="30"/>
-      <c r="D14" s="23"/>
-      <c r="E14" s="24"/>
+      <c r="A14" s="22"/>
+      <c r="B14" s="23"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="17"/>
     </row>
     <row r="15" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="29"/>
-      <c r="B15" s="30"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="24"/>
+      <c r="A15" s="22"/>
+      <c r="B15" s="23"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="17"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F1">
@@ -3371,7 +3305,7 @@
   <dimension ref="A1:F16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30" style="45" customWidth="1"/>
+    <col min="1" max="1" width="30" style="38" customWidth="1"/>
     <col min="2" max="2" width="36.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="5" width="30" customWidth="1"/>
     <col min="6" max="6" width="16" bestFit="1" customWidth="1"/>
@@ -3398,188 +3332,188 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A2" s="43" t="s">
+      <c r="A2" s="36" t="s">
         <v>225</v>
       </c>
-      <c r="B2" s="37" t="s">
+      <c r="B2" s="30" t="s">
         <v>238</v>
       </c>
       <c r="C2" s="2"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
       <c r="F2" s="2" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A3" s="43" t="s">
+      <c r="A3" s="36" t="s">
         <v>226</v>
       </c>
-      <c r="B3" s="37" t="s">
+      <c r="B3" s="30" t="s">
         <v>237</v>
       </c>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
       <c r="F3" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A4" s="43" t="s">
+      <c r="A4" s="36" t="s">
         <v>227</v>
       </c>
-      <c r="B4" s="37" t="s">
+      <c r="B4" s="30" t="s">
         <v>236</v>
       </c>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
       <c r="F4" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A5" s="43" t="s">
+      <c r="A5" s="36" t="s">
         <v>228</v>
       </c>
-      <c r="B5" s="37" t="s">
+      <c r="B5" s="30" t="s">
         <v>235</v>
       </c>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
       <c r="F5" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A6" s="43" t="s">
+      <c r="A6" s="36" t="s">
         <v>229</v>
       </c>
-      <c r="B6" s="37" t="s">
+      <c r="B6" s="30" t="s">
         <v>239</v>
       </c>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
       <c r="F6" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A7" s="43" t="s">
+      <c r="A7" s="36" t="s">
         <v>230</v>
       </c>
-      <c r="B7" s="37" t="s">
+      <c r="B7" s="30" t="s">
         <v>240</v>
       </c>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
       <c r="F7" t="str">
         <f>LOWER(A7)</f>
         <v>wordpress</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A8" s="43" t="s">
+      <c r="A8" s="36" t="s">
         <v>231</v>
       </c>
-      <c r="B8" s="37" t="s">
+      <c r="B8" s="30" t="s">
         <v>241</v>
       </c>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
       <c r="F8" t="str">
         <f t="shared" ref="F8:F10" si="0">LOWER(A8)</f>
         <v>shopify</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="45" t="s">
+      <c r="A9" s="38" t="s">
         <v>232</v>
       </c>
-      <c r="B9" s="37" t="s">
+      <c r="B9" s="30" t="s">
         <v>242</v>
       </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
       <c r="F9" t="str">
         <f t="shared" si="0"/>
         <v>flask</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A10" s="44" t="s">
+      <c r="A10" s="37" t="s">
         <v>233</v>
       </c>
-      <c r="B10" s="30" t="s">
+      <c r="B10" s="23" t="s">
         <v>243</v>
       </c>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
       <c r="F10" t="str">
         <f t="shared" si="0"/>
         <v>boostrap</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A11" s="44" t="s">
+      <c r="A11" s="37" t="s">
         <v>234</v>
       </c>
-      <c r="B11" s="30" t="s">
+      <c r="B11" s="23" t="s">
         <v>244</v>
       </c>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
       <c r="F11" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A12" s="44" t="s">
+      <c r="A12" s="37" t="s">
         <v>252</v>
       </c>
-      <c r="B12" s="30" t="s">
+      <c r="B12" s="23" t="s">
         <v>256</v>
       </c>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
       <c r="F12" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A13" s="44" t="s">
+      <c r="A13" s="37" t="s">
         <v>255</v>
       </c>
-      <c r="B13" s="30" t="s">
+      <c r="B13" s="23" t="s">
         <v>257</v>
       </c>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
       <c r="F13" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A14" s="44"/>
-      <c r="B14" s="30"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
+      <c r="A14" s="37"/>
+      <c r="B14" s="23"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10"/>
     </row>
     <row r="15" spans="1:6" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A15" s="44"/>
-      <c r="B15" s="30"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
+      <c r="A15" s="37"/>
+      <c r="B15" s="23"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
